--- a/erp-server/erp-server-file/src/main/resources/excel/wms/b2bThirdDeliveryExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/b2bThirdDeliveryExport.xlsx
@@ -97,7 +97,7 @@
     <t>{.soCode}</t>
   </si>
   <si>
-    <t>{.receiverName}</t>
+    <t>{.customerName}</t>
   </si>
   <si>
     <t>{.warehouseOrgName}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/b2bThirdDeliveryExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/b2bThirdDeliveryExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>发货单号</t>
   </si>
@@ -85,6 +85,9 @@
     <t>创建人</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>异常原因</t>
   </si>
   <si>
@@ -143,6 +146,9 @@
   </si>
   <si>
     <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
   </si>
   <si>
     <t>{.errorMessage}</t>
@@ -1112,7 +1118,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.625" customWidth="1"/>
@@ -1126,10 +1132,10 @@
     <col min="10" max="10" width="17.625" customWidth="1"/>
     <col min="11" max="11" width="15.25" customWidth="1"/>
     <col min="12" max="13" width="19.25" customWidth="1"/>
-    <col min="14" max="20" width="15.5" customWidth="1"/>
+    <col min="14" max="21" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:20">
+    <row r="1" customFormat="1" spans="1:21">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1190,67 +1196,73 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:21">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T2" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="U2" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/b2bThirdDeliveryExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/b2bThirdDeliveryExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>发货单号</t>
   </si>
@@ -155,6 +155,18 @@
   </si>
   <si>
     <t>{.pushTypeName}</t>
+  </si>
+  <si>
+    <t>平台订单编号</t>
+  </si>
+  <si>
+    <t>客户PO号</t>
+  </si>
+  <si>
+    <t>{.salesPlatformOrderCode}</t>
+  </si>
+  <si>
+    <t>{.customerPO}</t>
   </si>
 </sst>
 </file>
@@ -1118,150 +1130,164 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.625" customWidth="1"/>
     <col min="2" max="2" width="22.25" customWidth="1"/>
-    <col min="3" max="4" width="17.125" customWidth="1"/>
-    <col min="5" max="5" width="15.625" customWidth="1"/>
-    <col min="6" max="6" width="24.625" customWidth="1"/>
-    <col min="7" max="7" width="17.875" customWidth="1"/>
-    <col min="8" max="8" width="15.75" customWidth="1"/>
-    <col min="9" max="9" width="18.75" customWidth="1"/>
-    <col min="10" max="10" width="17.625" customWidth="1"/>
-    <col min="11" max="11" width="15.25" customWidth="1"/>
-    <col min="12" max="13" width="19.25" customWidth="1"/>
-    <col min="14" max="21" width="15.5" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="22.25" customWidth="1"/>
+    <col min="5" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
+    <col min="9" max="9" width="17.875" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="11" width="18.75" customWidth="1"/>
+    <col min="12" max="12" width="17.625" customWidth="1"/>
+    <col min="13" max="13" width="15.25" customWidth="1"/>
+    <col min="14" max="15" width="19.25" customWidth="1"/>
+    <col min="16" max="23" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:21">
+    <row r="1" customFormat="1" spans="1:23">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:23">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>25</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>27</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>28</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>29</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>30</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>31</v>
       </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>32</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>33</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>34</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>35</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>36</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>37</v>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>38</v>
       </c>
-      <c r="S2" t="s">
+      <c r="U2" t="s">
         <v>39</v>
       </c>
-      <c r="T2" t="s">
+      <c r="V2" t="s">
         <v>40</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>41</v>
       </c>
     </row>

--- a/erp-server/erp-server-file/src/main/resources/excel/wms/b2bThirdDeliveryExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/b2bThirdDeliveryExport.xlsx
@@ -1157,43 +1157,43 @@
         <v>42</v>
       </c>
       <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
         <v>43</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N1" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" t="s">
-        <v>12</v>
       </c>
       <c r="P1" t="s">
         <v>13</v>
@@ -1228,43 +1228,43 @@
         <v>44</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" t="s">
         <v>45</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" t="s">
-        <v>33</v>
       </c>
       <c r="P2" t="s">
         <v>34</v>
